--- a/file_upload_forms/047_uk_immigration_permission_to_stay_application_form--file_upload_forms.xlsx
+++ b/file_upload_forms/047_uk_immigration_permission_to_stay_application_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UK Immigration Permission To Stay Application Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the UK immigration permission to stay application form.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,18 +547,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_2</t>
+          <t>applicant_details_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Applicant Details</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +570,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_3</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Supporting Documents</t>
+          <t>Contact number?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +593,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_4</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E-Signature</t>
+          <t>Email address?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_5</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Date of birth?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_6</t>
+          <t>nationality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UK Permission To Stay Application Form</t>
+          <t>Nationality?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +662,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_7</t>
+          <t>passport_number</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Applicant Details 1</t>
+          <t>Passport number?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +685,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_8</t>
+          <t>uk_visa_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Applicant Details 2</t>
+          <t>UK visa or immigration status?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,58 +708,58 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_9</t>
+          <t>purpose_of_stay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Applicant Details 3</t>
+          <t>Purpose of stay?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_10</t>
+          <t>address_in_uk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E-Signature</t>
+          <t>Address in the UK?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_11</t>
+          <t>contact_address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Contact address (if different from the above address)?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +777,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_12</t>
+          <t>country_of_residence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E-Signature</t>
+          <t>Country of residence (outside the UK)?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,18 +800,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_13</t>
+          <t>address_in_uk_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Address in the UK (page 2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,87 +823,87 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_14</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Contact number (page 2)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_15</t>
+          <t>email_address_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Email address (page 2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_16</t>
+          <t>employment_details</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Employment details (page 3)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_17</t>
+          <t>education_details</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Education details (page 4-5)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -911,18 +915,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_18</t>
+          <t>work_travel_history</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Work/Travel history (page 6-7)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -934,18 +938,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_19</t>
+          <t>passport_scan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Passport scan (page 8)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,64 +961,64 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_20</t>
+          <t>id_scan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>ID scan (page 8)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_21</t>
+          <t>proof_of_employment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eSignature</t>
+          <t>Proof of employment (page 9)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_22</t>
+          <t>proof_of_education</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>e-Signature</t>
+          <t>Proof of education (page 10)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,18 +1030,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_23</t>
+          <t>proof_of_address</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>e-Signature</t>
+          <t>Proof of address (page 11)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1049,41 +1053,294 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_24</t>
+          <t>e_signature</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>e-Signature</t>
+          <t>E-signature</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_25</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>e-Signature</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>e_sign_date</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>E-sign date</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>e_signature_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>E-signature 2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>confirm_application</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Confirmation of application</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>submit_form</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Submission of the form</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>confirm_submission</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Review and confirm submission</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>final_signature</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Final signature</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>do_you_have_previous_immigration_issues</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Do you have any previous immigration issues?</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>do_you_have_any_health_issues</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Do you have any health issues?</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>do_you_have_any_dependents</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Do you have any dependents?</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dependents_details</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dependents' details</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>do_you_have_any_travel_history</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Do you have any travel history?</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1358,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1383,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_5_choices</t>
+          <t>e_signature_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1400,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_5_choices</t>
+          <t>e_signature_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1417,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_11_choices</t>
+          <t>do_you_have_previous_immigration_issues_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1434,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_11_choices</t>
+          <t>do_you_have_previous_immigration_issues_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_16_choices</t>
+          <t>do_you_have_any_health_issues_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1468,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_16_choices</t>
+          <t>do_you_have_any_health_issues_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1485,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_22_choices</t>
+          <t>do_you_have_any_dependents_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1502,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_22_choices</t>
+          <t>do_you_have_any_dependents_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1519,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_25_choices</t>
+          <t>do_you_have_any_travel_history_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1536,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>uk_immigration_permission_to_stay_application_form_page_25_choices</t>
+          <t>do_you_have_any_travel_history_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
